--- a/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 8,83</t>
+          <t>-1,8; 8,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 4,95</t>
+          <t>-7,15; 5,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,11</t>
+          <t>-6,55; 6,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,43</t>
+          <t>-4,24; 5,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 249,28</t>
+          <t>-24,8; 214,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 68,75</t>
+          <t>-50,6; 67,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,83; 86,05</t>
+          <t>-47,38; 94,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 238,49</t>
+          <t>-58,58; 204,52</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,67</t>
+          <t>-4,73; 4,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,94</t>
+          <t>-2,84; 7,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 9,38</t>
+          <t>0,04; 9,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,92</t>
+          <t>-7,21; 0,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 63,18</t>
+          <t>-39,76; 63,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 106,86</t>
+          <t>-25,33; 106,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 174,06</t>
+          <t>-2,85; 177,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 20,8</t>
+          <t>-70,9; 20,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 4,65</t>
+          <t>-5,27; 4,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 4,97</t>
+          <t>-6,48; 4,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 4,98</t>
+          <t>-6,53; 4,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,07</t>
+          <t>-4,25; 3,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,92; 94,05</t>
+          <t>-55,75; 105,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,59; 60,81</t>
+          <t>-46,87; 56,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 61,12</t>
+          <t>-48,87; 62,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,73; 115,45</t>
+          <t>-63,55; 136,91</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,38</t>
+          <t>-5,03; 4,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,83</t>
+          <t>-5,32; 4,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 4,39</t>
+          <t>-7,26; 3,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,56</t>
+          <t>-6,77; 1,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,93; 74,57</t>
+          <t>-46,63; 76,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,58; 83,11</t>
+          <t>-56,73; 92,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 56,37</t>
+          <t>-49,76; 45,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,45; 65,03</t>
+          <t>-81,75; 45,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,96</t>
+          <t>-1,99; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,38</t>
+          <t>-2,55; 2,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,39</t>
+          <t>-1,68; 3,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,54</t>
+          <t>-3,89; 0,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 43,16</t>
+          <t>-21,89; 40,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 29,64</t>
+          <t>-23,8; 34,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 40,05</t>
+          <t>-15,82; 41,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 12,44</t>
+          <t>-52,81; 12,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 8,59</t>
+          <t>-1,4; 8,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 5,1</t>
+          <t>-7,77; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 6,67</t>
+          <t>-6,24; 7,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,42</t>
+          <t>-3,98; 5,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 214,95</t>
+          <t>-25,35; 252,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,6; 67,01</t>
+          <t>-53,87; 59,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 94,35</t>
+          <t>-46,56; 96,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 204,52</t>
+          <t>-56,87; 209,94</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,49</t>
+          <t>-5,11; 4,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 7,15</t>
+          <t>-2,9; 7,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 9,81</t>
+          <t>-0,71; 9,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 0,99</t>
+          <t>-7,61; 0,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 63,47</t>
+          <t>-40,79; 66,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 106,98</t>
+          <t>-25,04; 109,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 177,35</t>
+          <t>-10,57; 164,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,9; 20,09</t>
+          <t>-69,61; 17,45</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,78</t>
+          <t>-5,44; 4,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 4,73</t>
+          <t>-6,6; 4,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,72</t>
+          <t>-6,54; 4,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 3,16</t>
+          <t>-4,49; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 105,7</t>
+          <t>-55,46; 87,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,87; 56,52</t>
+          <t>-46,59; 60,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 62,47</t>
+          <t>-49,4; 63,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 136,91</t>
+          <t>-67,51; 115,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 4,5</t>
+          <t>-4,62; 4,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,44</t>
+          <t>-5,1; 4,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 3,84</t>
+          <t>-6,6; 4,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,01</t>
+          <t>-6,92; 1,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,63; 76,86</t>
+          <t>-45,23; 72,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 92,84</t>
+          <t>-54,23; 91,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,76; 45,25</t>
+          <t>-45,34; 54,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,75; 45,29</t>
+          <t>-81,48; 57,59</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,86</t>
+          <t>-2,12; 2,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,8</t>
+          <t>-2,93; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,52</t>
+          <t>-1,77; 3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,51</t>
+          <t>-3,78; 0,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 40,7</t>
+          <t>-23,13; 38,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 34,93</t>
+          <t>-26,33; 30,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 41,19</t>
+          <t>-16,08; 39,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 12,39</t>
+          <t>-53,2; 7,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 8,68</t>
+          <t>-2,05; 8,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 5,04</t>
+          <t>-7,78; 4,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 7,0</t>
+          <t>-6,43; 6,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,53</t>
+          <t>-4,09; 5,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 252,4</t>
+          <t>-27,9; 249,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,87; 59,63</t>
+          <t>-51,81; 68,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 96,39</t>
+          <t>-47,83; 86,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,87; 209,94</t>
+          <t>-59,76; 241,79</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-37,87%</t>
+          <t>-38,42%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 4,64</t>
+          <t>-4,73; 4,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,48</t>
+          <t>-2,78; 6,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 9,18</t>
+          <t>-0,23; 9,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,83</t>
+          <t>-7,64; 0,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 66,75</t>
+          <t>-38,68; 63,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 109,01</t>
+          <t>-24,05; 106,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 164,34</t>
+          <t>-3,68; 174,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 17,45</t>
+          <t>-71,15; 19,42</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-9,31%</t>
+          <t>-0,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 4,24</t>
+          <t>-5,39; 4,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,71</t>
+          <t>-6,87; 4,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 4,84</t>
+          <t>-6,11; 4,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,3</t>
+          <t>-4,88; 4,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 87,43</t>
+          <t>-54,92; 94,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 60,01</t>
+          <t>-47,59; 60,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 63,86</t>
+          <t>-45,84; 61,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 115,43</t>
+          <t>-62,06; 145,8</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-44,23%</t>
+          <t>-46,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 4,42</t>
+          <t>-4,97; 4,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 4,19</t>
+          <t>-5,36; 3,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,26</t>
+          <t>-6,5; 4,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,1</t>
+          <t>-7,21; 1,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 72,09</t>
+          <t>-45,93; 74,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,23; 91,79</t>
+          <t>-54,58; 83,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 54,45</t>
+          <t>-46,78; 56,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,48; 57,59</t>
+          <t>-85,09; 54,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-27,53%</t>
+          <t>-25,49%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,7</t>
+          <t>-2,07; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,44</t>
+          <t>-2,77; 2,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,35</t>
+          <t>-1,81; 3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,4</t>
+          <t>-3,78; 0,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 38,11</t>
+          <t>-22,38; 43,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 30,69</t>
+          <t>-25,37; 29,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 39,56</t>
+          <t>-16,83; 40,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 7,53</t>
+          <t>-50,31; 12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-11,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.269223293094053</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.35208731377702</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1785654835272765</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.684179857511745</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.5624053668542391</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1187524483487002</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.01719538718527644</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1359891878419695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,05; 8,83</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,78; 4,95</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 6,11</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 5,98</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-27,9; 249,28</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-51,81; 68,75</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-47,83; 86,05</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-59,76; 241,79</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.050659739486014</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.78223414585784</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.433559880392563</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.091721999455988</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2790024402219137</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5180562925788642</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4783472938814345</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.597554624813456</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.832659788666003</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.946730244237438</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.110377142273522</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.976604621341688</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.492823378345423</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.6874919008638263</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.8605276141997388</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.417914700420264</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,26</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>58,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-38,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,73; 4,67</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,78; 6,94</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,23; 9,38</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,64; 0,87</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-38,68; 63,18</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-24,05; 106,86</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-3,68; 174,06</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-71,15; 19,42</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.14660779749706</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.983719037009545</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>4.261665664365831</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.036148088996496</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01523475320807987</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2198568222971947</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.5819755537506955</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3841663605002073</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-9,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-7,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,24%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.728153786318442</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.782798984956496</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.2283817660091762</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.640273733411485</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3867777568640344</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2405273640236101</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.03684556612444222</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7114501820335888</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,39; 4,65</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,87; 4,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,11; 4,98</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; 4,02</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-54,92; 94,05</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-47,59; 60,81</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-45,84; 61,12</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-62,06; 145,8</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.666462836822908</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.935053462723821</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.383102703458688</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.8708023572270355</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.631763158646632</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.068626216120383</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.740570150376978</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.194231845062743</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-6,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-11,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-46,31%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4295833767712406</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.043032295904236</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.7776187951399991</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.0122486820547961</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.05883976717457181</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.09326369948899323</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.07354570287937641</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.002417117023395379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,97; 4,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; 3,83</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,5; 4,39</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,21; 1,42</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-45,93; 74,57</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-54,58; 83,11</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-46,78; 56,37</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-85,09; 54,02</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.394082093051371</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.865110865327274</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.109995828626889</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.875227911419688</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5491926669904933</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4759475047737086</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4583720705733939</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6206229308559497</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.645937605614684</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.970302614042578</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.981430799255845</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.023746618247637</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9405381690639696</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.6080566013523918</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.6112304774792663</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.458000095315785</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.249233668838611</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.4359394646283751</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.230739299920204</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.665021641221312</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02987822750848187</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.06226655380935838</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1105031628403893</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4630798043519798</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.965242076100634</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.362426360912476</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.503642255742754</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.213705767738992</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4593434947449045</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5458173684617936</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4677501580959716</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.8508787342000922</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.380402715290941</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.831611053029644</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.391298095183807</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.415171498558121</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7456734793101036</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8310549324472674</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5637477015301553</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5401804670594071</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,88%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-25,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 2,96</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,77; 2,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 3,39</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 0,59</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-22,38; 43,16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,37; 29,64</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-16,83; 40,05</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-50,31; 12,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.4578927926325096</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.08242609409939011</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.787220284522247</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.575185453507531</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.05735881607826794</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.008758578226509476</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.08104671430221705</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2548705344317573</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.074660562929395</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.772867515356981</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.812628028949577</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.775262712553534</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2238291563756585</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2536738930799342</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1682623284933286</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5031394316382755</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.961332757354558</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.384031847157595</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.393424939764511</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.5918090908483898</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.431626800333319</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2964387090194573</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.400546664399573</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1202315819598125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
